--- a/artfynd/A 27603-2025 artfynd.xlsx
+++ b/artfynd/A 27603-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132343581</v>
+        <v>132343166</v>
       </c>
       <c r="B2" t="n">
-        <v>80475</v>
+        <v>80489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>416782</v>
+        <v>416914</v>
       </c>
       <c r="R2" t="n">
-        <v>6971916</v>
+        <v>6971882</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132344573</v>
+        <v>132343581</v>
       </c>
       <c r="B3" t="n">
-        <v>80474</v>
+        <v>80489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416833</v>
+        <v>416782</v>
       </c>
       <c r="R3" t="n">
-        <v>6971582</v>
+        <v>6971916</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132344325</v>
+        <v>132344573</v>
       </c>
       <c r="B4" t="n">
-        <v>79117</v>
+        <v>80488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416779</v>
+        <v>416833</v>
       </c>
       <c r="R4" t="n">
-        <v>6971721</v>
+        <v>6971582</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +963,103 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132344325</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vallhall, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>416779</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6971721</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27603-2025 artfynd.xlsx
+++ b/artfynd/A 27603-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132343166</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132343581</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132344573</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132344325</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27603-2025 artfynd.xlsx
+++ b/artfynd/A 27603-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,45 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132343166</v>
+        <v>135784692</v>
       </c>
       <c r="B2" t="n">
-        <v>80489</v>
+        <v>92227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vallhall, Hjd</t>
+          <t>Lövdalen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>416914</v>
+        <v>416917</v>
       </c>
       <c r="R2" t="n">
-        <v>6971882</v>
+        <v>6971559</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,24 +765,24 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132343166</t>
+          <t>https://artportalen.se/Sighting/135784692</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132343581</v>
+        <v>132343166</v>
       </c>
       <c r="B3" t="n">
         <v>80489</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416782</v>
+        <v>416914</v>
       </c>
       <c r="R3" t="n">
-        <v>6971916</v>
+        <v>6971882</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,16 +878,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132343581</t>
+          <t>https://artportalen.se/Sighting/132343166</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132344573</v>
+        <v>132343581</v>
       </c>
       <c r="B4" t="n">
-        <v>80488</v>
+        <v>80489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416833</v>
+        <v>416782</v>
       </c>
       <c r="R4" t="n">
-        <v>6971582</v>
+        <v>6971916</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,16 +980,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132344573</t>
+          <t>https://artportalen.se/Sighting/132343581</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132344325</v>
+        <v>135784691</v>
       </c>
       <c r="B5" t="n">
-        <v>79131</v>
+        <v>78844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vallhall, Hjd</t>
+          <t>Lövdalen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>416779</v>
+        <v>416907</v>
       </c>
       <c r="R5" t="n">
-        <v>6971721</v>
+        <v>6971607</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,18 +1071,630 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135784691</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135784690</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>416907</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6971608</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784690</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135784694</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>416912</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6971553</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784694</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132344573</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vallhall, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>416833</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6971582</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132344573</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135784695</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>416833</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6971573</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784695</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132344325</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vallhall, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>416779</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6971721</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/132344325</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135784693</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>416913</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6971552</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784693</t>
         </is>
       </c>
     </row>
@@ -1092,6 +1704,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27603-2025 artfynd.xlsx
+++ b/artfynd/A 27603-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784692</v>
       </c>
       <c r="B2" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27603-2025 artfynd.xlsx
+++ b/artfynd/A 27603-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784692</v>
       </c>
       <c r="B2" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784691</v>
       </c>
       <c r="B5" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784690</v>
       </c>
       <c r="B6" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135784694</v>
       </c>
       <c r="B7" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784695</v>
       </c>
       <c r="B9" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135784693</v>
       </c>
       <c r="B11" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27603-2025 artfynd.xlsx
+++ b/artfynd/A 27603-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784692</v>
       </c>
       <c r="B2" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784691</v>
       </c>
       <c r="B5" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784690</v>
       </c>
       <c r="B6" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135784694</v>
       </c>
       <c r="B7" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784695</v>
       </c>
       <c r="B9" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135784693</v>
       </c>
       <c r="B11" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27603-2025 artfynd.xlsx
+++ b/artfynd/A 27603-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784692</v>
       </c>
       <c r="B2" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27603-2025 artfynd.xlsx
+++ b/artfynd/A 27603-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784692</v>
       </c>
       <c r="B2" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784691</v>
       </c>
       <c r="B5" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784690</v>
       </c>
       <c r="B6" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135784694</v>
       </c>
       <c r="B7" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784695</v>
       </c>
       <c r="B9" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135784693</v>
       </c>
       <c r="B11" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27603-2025 artfynd.xlsx
+++ b/artfynd/A 27603-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784692</v>
       </c>
       <c r="B2" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784691</v>
       </c>
       <c r="B5" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784690</v>
       </c>
       <c r="B6" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135784694</v>
       </c>
       <c r="B7" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784695</v>
       </c>
       <c r="B9" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135784693</v>
       </c>
       <c r="B11" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27603-2025 artfynd.xlsx
+++ b/artfynd/A 27603-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784692</v>
       </c>
       <c r="B2" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784691</v>
       </c>
       <c r="B5" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784690</v>
       </c>
       <c r="B6" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135784694</v>
       </c>
       <c r="B7" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784695</v>
       </c>
       <c r="B9" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135784693</v>
       </c>
       <c r="B11" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27603-2025 artfynd.xlsx
+++ b/artfynd/A 27603-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784692</v>
       </c>
       <c r="B2" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784691</v>
       </c>
       <c r="B5" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784690</v>
       </c>
       <c r="B6" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135784694</v>
       </c>
       <c r="B7" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784695</v>
       </c>
       <c r="B9" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135784693</v>
       </c>
       <c r="B11" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27603-2025 artfynd.xlsx
+++ b/artfynd/A 27603-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784692</v>
       </c>
       <c r="B2" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784691</v>
       </c>
       <c r="B5" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784690</v>
       </c>
       <c r="B6" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135784694</v>
       </c>
       <c r="B7" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135784695</v>
       </c>
       <c r="B9" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135784693</v>
       </c>
       <c r="B11" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27603-2025 artfynd.xlsx
+++ b/artfynd/A 27603-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784692</v>
       </c>
       <c r="B2" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
